--- a/resources/templates/work_experience/work_experience.xlsx
+++ b/resources/templates/work_experience/work_experience.xlsx
@@ -1,57 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Herd\hrcms\resources\templates\work_experience\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F20D522-D8BE-495E-B7C9-31842B6885B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38670" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
-  <si>
-    <t>institution</t>
-  </si>
-  <si>
-    <t>position</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="6">
+  <si>
+    <t>institution_ka</t>
+  </si>
+  <si>
+    <t>institution_en</t>
+  </si>
+  <si>
+    <t>position_ka</t>
+  </si>
+  <si>
+    <t>position_en</t>
   </si>
   <si>
     <t>started_at</t>
   </si>
   <si>
-    <t>instu 2</t>
-  </si>
-  <si>
-    <t>test 1</t>
+    <t>ended_at</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -74,24 +71,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="1">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -381,14 +368,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -399,162 +386,27 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2">
-        <v>45411</v>
-      </c>
-      <c r="D2" s="2">
-        <v>46141</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>